--- a/data/gonna_be_goldfish.xlsx
+++ b/data/gonna_be_goldfish.xlsx
@@ -8,21 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tom\Documents\website\rhytididae\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CBD0BE-6556-45BA-8072-5FBE0E8A00FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0C139C-C600-41A8-BA85-E3EDD34A0345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
     <sheet name="Summary " sheetId="2" r:id="rId2"/>
     <sheet name="Responses" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="217">
   <si>
     <t>Survey Name</t>
   </si>
@@ -569,6 +583,111 @@
   </si>
   <si>
     <t>5.10m</t>
+  </si>
+  <si>
+    <t>In game minion power</t>
+  </si>
+  <si>
+    <t>Pengu</t>
+  </si>
+  <si>
+    <t>DeezNutz</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>whelp</t>
+  </si>
+  <si>
+    <t>PermeatingMass</t>
+  </si>
+  <si>
+    <t>Kilosaw</t>
+  </si>
+  <si>
+    <t>Rockbadger32</t>
+  </si>
+  <si>
+    <t>Traveler10468</t>
+  </si>
+  <si>
+    <t>Keanu</t>
+  </si>
+  <si>
+    <t>FlameFun</t>
+  </si>
+  <si>
+    <t>SirCraig</t>
+  </si>
+  <si>
+    <t>Hody</t>
+  </si>
+  <si>
+    <t>Delirium</t>
+  </si>
+  <si>
+    <t>Paperfish</t>
+  </si>
+  <si>
+    <t>Kubisk</t>
+  </si>
+  <si>
+    <t>Kierly</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>Envoy</t>
+  </si>
+  <si>
+    <t>Wanderson</t>
+  </si>
+  <si>
+    <t>mrSnailio</t>
+  </si>
+  <si>
+    <t>Kaiju</t>
+  </si>
+  <si>
+    <t>colby</t>
+  </si>
+  <si>
+    <t>lampside</t>
+  </si>
+  <si>
+    <t>wilsperho</t>
+  </si>
+  <si>
+    <t>gingerred</t>
+  </si>
+  <si>
+    <t>obijimbob</t>
+  </si>
+  <si>
+    <t>smoke</t>
+  </si>
+  <si>
+    <t>Traveler1</t>
+  </si>
+  <si>
+    <t>callmemaui</t>
+  </si>
+  <si>
+    <t>snaillord2023</t>
+  </si>
+  <si>
+    <t>demonsnailjoey</t>
+  </si>
+  <si>
+    <t>howlinghati</t>
+  </si>
+  <si>
+    <t>AVE</t>
+  </si>
+  <si>
+    <t>*</t>
   </si>
 </sst>
 </file>
@@ -593,12 +712,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -613,15 +750,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -632,6 +779,25 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E09D0B3C-0044-486E-876C-A67FF78BD974}" name="Table3" displayName="Table3" ref="B1:F55" totalsRowShown="0">
+  <autoFilter ref="B1:F55" xr:uid="{E09D0B3C-0044-486E-876C-A67FF78BD974}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F55">
+    <sortCondition descending="1" ref="C1:C55"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{9E92AEF5-521A-402A-AEF9-8891BECD34DD}" name="Nick"/>
+    <tableColumn id="2" xr3:uid="{4D6ED905-5AEC-477E-9AFD-5CBFB5EDD7D2}" name="What is your deployed minion power in the nursery room fridge?" dataDxfId="0">
+      <calculatedColumnFormula>(E2*$G$2)/1000000</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{47739183-599B-40AE-BEC3-C1196DD99537}" name="What is your snails total power?"/>
+    <tableColumn id="4" xr3:uid="{F5F92D63-9540-46E6-965A-7D034FCD03BF}" name="In game minion power"/>
+    <tableColumn id="5" xr3:uid="{2176E26E-28C1-4D54-AA7F-F292F8B8F63E}" name="Ratio"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2302,7 +2468,7 @@
       <c r="G24" t="s">
         <v>81</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24">
         <v>339212836</v>
       </c>
       <c r="I24">
@@ -2313,4 +2479,847 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F9787F4-2FF6-43FE-8E72-B92E5C801FF4}">
+  <dimension ref="A1:G55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="49" customWidth="1"/>
+    <col min="4" max="4" width="31" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2">
+        <v>14827331</v>
+      </c>
+      <c r="F2">
+        <f>(C2*1000000)/E2</f>
+        <v>0.6717324918422608</v>
+      </c>
+      <c r="G2">
+        <f>(SUM(F2:F24)/23)</f>
+        <v>0.40453268278145144</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3">
+        <v>13369284</v>
+      </c>
+      <c r="F3">
+        <f>(C3*1000000)/E3</f>
+        <v>0.68216069013119929</v>
+      </c>
+      <c r="G3">
+        <v>0.73337232092693083</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4">
+        <v>8.09</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4">
+        <v>12618368</v>
+      </c>
+      <c r="F4">
+        <f>(C4*1000000)/E4</f>
+        <v>0.64112886864608798</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="3">
+        <f>(E5*$G$3)/1000000</f>
+        <v>6.6698159145805764</v>
+      </c>
+      <c r="E5">
+        <v>9094720</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6">
+        <v>6.62</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6">
+        <v>9227816</v>
+      </c>
+      <c r="F6">
+        <f>(C6*1000000)/E6</f>
+        <v>0.71739618561965257</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="3">
+        <f>(E7*$G$3)/1000000</f>
+        <v>6.5283373932889575</v>
+      </c>
+      <c r="E7">
+        <v>8901805</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8">
+        <v>5.84</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8">
+        <v>7788872</v>
+      </c>
+      <c r="F8">
+        <f>(C8*1000000)/E8</f>
+        <v>0.74978764575923185</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="3">
+        <f>(E9*$G$3)/1000000</f>
+        <v>5.7347134025916331</v>
+      </c>
+      <c r="E9">
+        <v>7819648</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10">
+        <v>5.72</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10">
+        <v>8417565</v>
+      </c>
+      <c r="F10">
+        <f>(C10*1000000)/E10</f>
+        <v>0.67953143218971279</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11">
+        <v>5.68</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11">
+        <v>7984829</v>
+      </c>
+      <c r="F11">
+        <f>(C11*1000000)/E11</f>
+        <v>0.71134898443034911</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="3">
+        <f>(E12*$G$3)/1000000</f>
+        <v>5.6072063573859934</v>
+      </c>
+      <c r="E12">
+        <v>7645784</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13">
+        <v>5.52</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13">
+        <v>7072034</v>
+      </c>
+      <c r="F13">
+        <f>(C13*1000000)/E13</f>
+        <v>0.78053923383286905</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14">
+        <v>5.32</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14">
+        <v>7645784</v>
+      </c>
+      <c r="F14">
+        <f>(C14*1000000)/E14</f>
+        <v>0.6958083042890042</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D15" s="2">
+        <v>339212836</v>
+      </c>
+      <c r="E15">
+        <v>6940857</v>
+      </c>
+      <c r="F15">
+        <f>(C15*1000000)/E15</f>
+        <v>0.7347795812534389</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16">
+        <v>4.92</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16">
+        <v>6992175</v>
+      </c>
+      <c r="F16">
+        <f>(C16*1000000)/E16</f>
+        <v>0.70364371601111242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C17" s="3">
+        <f>(E17*$G$3)/1000000</f>
+        <v>4.8426187769911282</v>
+      </c>
+      <c r="E17">
+        <v>6603220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="3">
+        <f>(E18*$G$3)/1000000</f>
+        <v>4.8016863342709124</v>
+      </c>
+      <c r="E18">
+        <v>6547406</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C19" s="3">
+        <f>(E19*$G$3)/1000000</f>
+        <v>4.7929665373750918</v>
+      </c>
+      <c r="E19">
+        <v>6535516</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20">
+        <v>4.75</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20">
+        <v>6278769</v>
+      </c>
+      <c r="F20">
+        <f>(C20*1000000)/E20</f>
+        <v>0.75651771868020623</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="3">
+        <f>(E21*$G$3)/1000000</f>
+        <v>4.7243940252514607</v>
+      </c>
+      <c r="E21">
+        <v>6442013</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C22" s="3">
+        <f>(E22*$G$3)/1000000</f>
+        <v>4.7089653383637993</v>
+      </c>
+      <c r="E22">
+        <v>6420975</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C23" s="3">
+        <f>(E23*$G$3)/1000000</f>
+        <v>4.614884670173689</v>
+      </c>
+      <c r="E23">
+        <v>6292690</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C24">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24">
+        <v>5847077</v>
+      </c>
+      <c r="F24">
+        <f>(C24*1000000)/E24</f>
+        <v>0.77987685128825912</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>216</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="3">
+        <f>(E25*$G$3)/1000000</f>
+        <v>4.5482988636674486</v>
+      </c>
+      <c r="E25">
+        <v>6201896</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C26" s="3">
+        <f>(E26*$G$3)/1000000</f>
+        <v>4.5421664043198575</v>
+      </c>
+      <c r="E26">
+        <v>6193534</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C27" s="3">
+        <f>(E27*$G$3)/1000000</f>
+        <v>4.4317285998837921</v>
+      </c>
+      <c r="E27">
+        <v>6042945</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C28" s="3">
+        <f>(E28*$G$3)/1000000</f>
+        <v>4.4019426830693442</v>
+      </c>
+      <c r="E28">
+        <v>6002330</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29">
+        <v>5890384</v>
+      </c>
+      <c r="F29">
+        <f>(C29*1000000)/E29</f>
+        <v>0.74698016292316427</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C30" s="3">
+        <f>(E30*$G$3)/1000000</f>
+        <v>4.3016994872664842</v>
+      </c>
+      <c r="E30">
+        <v>5865642</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C31" s="3">
+        <f>(E31*$G$3)/1000000</f>
+        <v>4.2251156159090471</v>
+      </c>
+      <c r="E31">
+        <v>5761215</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32">
+        <v>4.21</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32">
+        <v>5654465</v>
+      </c>
+      <c r="F32">
+        <f>(C32*1000000)/E32</f>
+        <v>0.74454435565522115</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33">
+        <v>4.21</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33">
+        <v>5610901</v>
+      </c>
+      <c r="F33">
+        <f>(C33*1000000)/E33</f>
+        <v>0.75032512603590762</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>216</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C34" s="3">
+        <f>(E34*$G$3)/1000000</f>
+        <v>4.1258492720376623</v>
+      </c>
+      <c r="E34">
+        <v>5625859</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C35" s="3">
+        <f>(E35*$G$3)/1000000</f>
+        <v>4.0043778810332507</v>
+      </c>
+      <c r="E35">
+        <v>5460225</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36">
+        <v>3.86</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36">
+        <v>5429215</v>
+      </c>
+      <c r="F36">
+        <f>(C36*1000000)/E36</f>
+        <v>0.71096834441074819</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C37" s="3">
+        <f>(E37*$G$3)/1000000</f>
+        <v>3.8138257508868061</v>
+      </c>
+      <c r="E37">
+        <v>5200395</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C38" s="3">
+        <f>(E38*$G$3)/1000000</f>
+        <v>3.7964917627093775</v>
+      </c>
+      <c r="E38">
+        <v>5176759</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B39" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C39" s="3">
+        <f>(E39*$G$3)/1000000</f>
+        <v>3.7404005141156023</v>
+      </c>
+      <c r="E39">
+        <v>5100275</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B40" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C40">
+        <v>3.74</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40">
+        <v>4885125</v>
+      </c>
+      <c r="F40">
+        <f>(C40*1000000)/E40</f>
+        <v>0.76558941685217885</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B41" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C41">
+        <v>3.65</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41">
+        <v>4782975</v>
+      </c>
+      <c r="F41">
+        <f>(C41*1000000)/E41</f>
+        <v>0.7631233698691714</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B42" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C42" s="3">
+        <f>(E42*$G$3)/1000000</f>
+        <v>3.6499295044890929</v>
+      </c>
+      <c r="E42">
+        <v>4976912</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B43" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C43" s="3">
+        <f>(E43*$G$3)/1000000</f>
+        <v>3.6139172566699762</v>
+      </c>
+      <c r="E43">
+        <v>4927807</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B44" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C44" s="3">
+        <f>(E44*$G$3)/1000000</f>
+        <v>3.521551946338513</v>
+      </c>
+      <c r="E44">
+        <v>4801861</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B45" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C45">
+        <v>3.5</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45">
+        <v>4700964</v>
+      </c>
+      <c r="F45">
+        <f>(C45*1000000)/E45</f>
+        <v>0.74452814358927233</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>216</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C46" s="3">
+        <f>(E46*$G$3)/1000000</f>
+        <v>3.4421401913115819</v>
+      </c>
+      <c r="E46">
+        <v>4693578</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C47" s="3">
+        <f>(E47*$G$3)/1000000</f>
+        <v>3.4313244163225516</v>
+      </c>
+      <c r="E47">
+        <v>4678830</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C48" s="3">
+        <f>(E48*$G$3)/1000000</f>
+        <v>3.1756876928108051</v>
+      </c>
+      <c r="E48">
+        <v>4330253</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B49" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C49" s="3">
+        <f>(E49*$G$3)/1000000</f>
+        <v>2.679152095948659</v>
+      </c>
+      <c r="E49">
+        <v>3653195</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B50" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C50">
+        <v>2.6</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50">
+        <v>3162943</v>
+      </c>
+      <c r="F50">
+        <f>(C50*1000000)/E50</f>
+        <v>0.82201923967646584</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B51" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C51" s="3">
+        <f>(E51*$G$3)/1000000</f>
+        <v>2.2790058233429025</v>
+      </c>
+      <c r="E51">
+        <v>3107570</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B52" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E52">
+        <v>2549059</v>
+      </c>
+      <c r="F52">
+        <f>(C52*1000000)/E52</f>
+        <v>0.79637230836948059</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B53" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C53">
+        <v>2.02</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E53">
+        <v>2810000</v>
+      </c>
+      <c r="F53">
+        <f>(C53*1000000)/E53</f>
+        <v>0.71886120996441283</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B54" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C54" s="3">
+        <f>(E54*$G$3)/1000000</f>
+        <v>1.9754798872746271</v>
+      </c>
+      <c r="E54">
+        <v>2693693</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B55" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C55" s="3">
+        <f>(E55*$G$3)/1000000</f>
+        <v>1.2709995023029337</v>
+      </c>
+      <c r="E55">
+        <v>1733089</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>